--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4714-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4714-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC647FA1-3760-489C-B4E0-D27A53D03D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C439E556-5F8C-44CC-8BE6-88F967574B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{086BF399-98AD-4EA5-AB2A-7B9C48B011CC}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B65F8B37-1EC8-479A-86D2-3DFC71A67C3E}"/>
   </bookViews>
   <sheets>
     <sheet name="4714-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1574,28 +1574,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E687401-8854-44BD-9D66-8FA9DA9BE1AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE07791D-DB66-4025-85AD-BFC4347ACACD}">
   <dimension ref="A1:X50"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="W1" s="33"/>
       <c r="X1" s="25"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1665,7 +1665,7 @@
       <c r="W2" s="35"/>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="X3" s="39"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1785,7 +1785,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="40">
         <v>2025</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="42">
         <v>2024</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2023</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="42">
         <v>2022</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2021</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="42">
         <v>2020</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="44">
         <v>2019</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>9.69</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="46"/>
       <c r="B23" s="47"/>
       <c r="C23" s="20" t="s">
@@ -3131,7 +3131,7 @@
       <c r="W23" s="53"/>
       <c r="X23" s="49"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="50" t="s">
         <v>29</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>9.69</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="51"/>
       <c r="B25" s="51"/>
       <c r="C25" s="22" t="s">
@@ -3233,7 +3233,7 @@
       <c r="W25" s="53"/>
       <c r="X25" s="49"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="42">
         <v>2018</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2017</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="42">
         <v>2016</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>2015</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="42">
         <v>2014</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>2013</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42">
         <v>2012</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
         <v>2011</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="42">
         <v>2010</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="40">
         <v>2009</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="42">
         <v>2008</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="40">
         <v>2007</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="42">
         <v>2006</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
         <v>2005</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="42">
         <v>2004</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="40">
         <v>2003</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="42">
         <v>2002</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="40">
         <v>2001</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="42">
         <v>2000</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <v>1999</v>
       </c>
@@ -4747,7 +4747,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="42">
         <v>1998</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <v>1997</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="42">
         <v>1996</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="40" t="s">
         <v>62</v>
       </c>
